--- a/artfynd/A 42971-2026 artfynd.xlsx
+++ b/artfynd/A 42971-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934385</v>
       </c>
       <c r="B2" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>136934382</v>
       </c>
       <c r="B31" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>136934383</v>
       </c>
       <c r="B32" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>136934384</v>
       </c>
       <c r="B33" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>136934387</v>
       </c>
       <c r="B34" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>136934388</v>
       </c>
       <c r="B35" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>136934389</v>
       </c>
       <c r="B36" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>136934390</v>
       </c>
       <c r="B37" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>136934391</v>
       </c>
       <c r="B38" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>136934392</v>
       </c>
       <c r="B39" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>136934396</v>
       </c>
       <c r="B40" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>136934398</v>
       </c>
       <c r="B41" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 42971-2026 artfynd.xlsx
+++ b/artfynd/A 42971-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934385</v>
       </c>
       <c r="B2" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>136934394</v>
       </c>
       <c r="B11" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>136934397</v>
       </c>
       <c r="B13" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>136934382</v>
       </c>
       <c r="B31" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>136934383</v>
       </c>
       <c r="B32" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>136934384</v>
       </c>
       <c r="B33" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>136934387</v>
       </c>
       <c r="B34" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>136934388</v>
       </c>
       <c r="B35" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>136934389</v>
       </c>
       <c r="B36" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>136934390</v>
       </c>
       <c r="B37" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>136934391</v>
       </c>
       <c r="B38" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>136934392</v>
       </c>
       <c r="B39" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>136934396</v>
       </c>
       <c r="B40" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>136934398</v>
       </c>
       <c r="B41" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 42971-2026 artfynd.xlsx
+++ b/artfynd/A 42971-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934385</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>136934382</v>
       </c>
       <c r="B31" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>136934383</v>
       </c>
       <c r="B32" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>136934384</v>
       </c>
       <c r="B33" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>136934387</v>
       </c>
       <c r="B34" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>136934388</v>
       </c>
       <c r="B35" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>136934389</v>
       </c>
       <c r="B36" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>136934390</v>
       </c>
       <c r="B37" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>136934391</v>
       </c>
       <c r="B38" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>136934392</v>
       </c>
       <c r="B39" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>136934396</v>
       </c>
       <c r="B40" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>136934398</v>
       </c>
       <c r="B41" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 42971-2026 artfynd.xlsx
+++ b/artfynd/A 42971-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934385</v>
       </c>
       <c r="B2" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>136934394</v>
       </c>
       <c r="B11" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>136934397</v>
       </c>
       <c r="B13" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>136934382</v>
       </c>
       <c r="B31" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>136934383</v>
       </c>
       <c r="B32" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>136934384</v>
       </c>
       <c r="B33" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>136934387</v>
       </c>
       <c r="B34" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>136934388</v>
       </c>
       <c r="B35" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>136934389</v>
       </c>
       <c r="B36" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>136934390</v>
       </c>
       <c r="B37" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>136934391</v>
       </c>
       <c r="B38" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>136934392</v>
       </c>
       <c r="B39" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>136934396</v>
       </c>
       <c r="B40" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>136934398</v>
       </c>
       <c r="B41" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 42971-2026 artfynd.xlsx
+++ b/artfynd/A 42971-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ41"/>
+  <dimension ref="A1:AZ54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136934385</v>
       </c>
       <c r="B2" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>136934382</v>
       </c>
       <c r="B31" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>136934383</v>
       </c>
       <c r="B32" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>136934384</v>
       </c>
       <c r="B33" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>136934387</v>
       </c>
       <c r="B34" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>136934388</v>
       </c>
       <c r="B35" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>136934389</v>
       </c>
       <c r="B36" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>136934390</v>
       </c>
       <c r="B37" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>136934391</v>
       </c>
       <c r="B38" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>136934392</v>
       </c>
       <c r="B39" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>136934396</v>
       </c>
       <c r="B40" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>136934398</v>
       </c>
       <c r="B41" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5404,6 +5404,1542 @@
       <c r="AZ41" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136934398</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>137381620</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99412</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Gravertjärnen Valsan 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>516149</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6721065</v>
+      </c>
+      <c r="S42" t="n">
+        <v>8</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>10 plantor</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137381620</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>137381622</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99412</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Gravertjärnen Valsan 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>516131</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6721050</v>
+      </c>
+      <c r="S43" t="n">
+        <v>14</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>50 plantor</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137381622</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>137381623</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99412</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Gravertjärnen Valsan 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>516123</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6721073</v>
+      </c>
+      <c r="S44" t="n">
+        <v>16</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>20 plantor</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137381623</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>137381626</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99412</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Gravertjärnen Valsan 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>516079</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6721087</v>
+      </c>
+      <c r="S45" t="n">
+        <v>26</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>10 plantor</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137381626</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>137381627</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99412</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Gravertjärnen Valsan 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>516096</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6721124</v>
+      </c>
+      <c r="S46" t="n">
+        <v>9</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>10 plantor</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137381627</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>137381628</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99412</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Gravertjärnen Valsan 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>516120</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6721113</v>
+      </c>
+      <c r="S47" t="n">
+        <v>14</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>100 plantor</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137381628</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>137381629</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99412</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Gravertjärnen Valsan 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>516126</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6721144</v>
+      </c>
+      <c r="S48" t="n">
+        <v>8</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>30 plantor</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137381629</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>137381630</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99412</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Gravertjärnen Valsan 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>516134</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6721137</v>
+      </c>
+      <c r="S49" t="n">
+        <v>7</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>30 plantor</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137381630</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>137381632</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99412</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Gravertjärnen Valsan 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>516180</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6721159</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>20 plantor</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137381632</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>137381634</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99412</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Gravertjärnen Valsan 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>516060</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6721175</v>
+      </c>
+      <c r="S51" t="n">
+        <v>11</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>20 plantor</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137381634</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>137381635</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99412</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Gravertjärnen Valsan 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>516050</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6721187</v>
+      </c>
+      <c r="S52" t="n">
+        <v>8</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>20 plantor</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137381635</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>137381636</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99412</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Gravertjärnen Valsan 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>515726</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6721296</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>20 st</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137381636</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>137381625</v>
+      </c>
+      <c r="B54" t="n">
+        <v>98280</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Gravertjärnen Valsan 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>516116</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6721082</v>
+      </c>
+      <c r="S54" t="n">
+        <v>11</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>1 m2</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137381625</t>
         </is>
       </c>
     </row>
@@ -5449,6 +6985,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42971-2026 artfynd.xlsx
+++ b/artfynd/A 42971-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934385</v>
       </c>
       <c r="B2" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>136934394</v>
       </c>
       <c r="B11" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>136934397</v>
       </c>
       <c r="B13" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>136934382</v>
       </c>
       <c r="B31" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>136934383</v>
       </c>
       <c r="B32" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>136934384</v>
       </c>
       <c r="B33" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>136934387</v>
       </c>
       <c r="B34" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>136934388</v>
       </c>
       <c r="B35" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>136934389</v>
       </c>
       <c r="B36" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>136934390</v>
       </c>
       <c r="B37" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>136934391</v>
       </c>
       <c r="B38" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>136934392</v>
       </c>
       <c r="B39" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>136934396</v>
       </c>
       <c r="B40" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>136934398</v>
       </c>
       <c r="B41" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>137381620</v>
       </c>
       <c r="B42" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>137381622</v>
       </c>
       <c r="B43" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>137381623</v>
       </c>
       <c r="B44" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>137381626</v>
       </c>
       <c r="B45" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         <v>137381627</v>
       </c>
       <c r="B46" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>137381628</v>
       </c>
       <c r="B47" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         <v>137381629</v>
       </c>
       <c r="B48" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>137381630</v>
       </c>
       <c r="B49" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>137381632</v>
       </c>
       <c r="B50" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>137381634</v>
       </c>
       <c r="B51" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>137381635</v>
       </c>
       <c r="B52" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>137381636</v>
       </c>
       <c r="B53" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>137381625</v>
       </c>
       <c r="B54" t="n">
-        <v>98280</v>
+        <v>98286</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 42971-2026 artfynd.xlsx
+++ b/artfynd/A 42971-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934385</v>
       </c>
       <c r="B2" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>136934394</v>
       </c>
       <c r="B11" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>136934382</v>
       </c>
       <c r="B31" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>136934383</v>
       </c>
       <c r="B32" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>136934384</v>
       </c>
       <c r="B33" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>136934387</v>
       </c>
       <c r="B34" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>136934388</v>
       </c>
       <c r="B35" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>136934389</v>
       </c>
       <c r="B36" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>136934390</v>
       </c>
       <c r="B37" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>136934391</v>
       </c>
       <c r="B38" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>136934392</v>
       </c>
       <c r="B39" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>136934396</v>
       </c>
       <c r="B40" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>136934398</v>
       </c>
       <c r="B41" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>137381620</v>
       </c>
       <c r="B42" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>137381622</v>
       </c>
       <c r="B43" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>137381623</v>
       </c>
       <c r="B44" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>137381626</v>
       </c>
       <c r="B45" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         <v>137381627</v>
       </c>
       <c r="B46" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>137381628</v>
       </c>
       <c r="B47" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         <v>137381629</v>
       </c>
       <c r="B48" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>137381630</v>
       </c>
       <c r="B49" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>137381632</v>
       </c>
       <c r="B50" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>137381634</v>
       </c>
       <c r="B51" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>137381635</v>
       </c>
       <c r="B52" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>137381636</v>
       </c>
       <c r="B53" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>137381625</v>
       </c>
       <c r="B54" t="n">
-        <v>98286</v>
+        <v>98298</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 42971-2026 artfynd.xlsx
+++ b/artfynd/A 42971-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934385</v>
       </c>
       <c r="B2" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>136934394</v>
       </c>
       <c r="B11" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>136934382</v>
       </c>
       <c r="B31" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>136934383</v>
       </c>
       <c r="B32" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>136934384</v>
       </c>
       <c r="B33" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>136934387</v>
       </c>
       <c r="B34" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>136934388</v>
       </c>
       <c r="B35" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>136934389</v>
       </c>
       <c r="B36" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>136934390</v>
       </c>
       <c r="B37" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>136934391</v>
       </c>
       <c r="B38" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>136934392</v>
       </c>
       <c r="B39" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>136934396</v>
       </c>
       <c r="B40" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>136934398</v>
       </c>
       <c r="B41" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>137381620</v>
       </c>
       <c r="B42" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>137381622</v>
       </c>
       <c r="B43" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>137381623</v>
       </c>
       <c r="B44" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>137381626</v>
       </c>
       <c r="B45" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         <v>137381627</v>
       </c>
       <c r="B46" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>137381628</v>
       </c>
       <c r="B47" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         <v>137381629</v>
       </c>
       <c r="B48" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>137381630</v>
       </c>
       <c r="B49" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>137381632</v>
       </c>
       <c r="B50" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>137381634</v>
       </c>
       <c r="B51" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>137381635</v>
       </c>
       <c r="B52" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>137381636</v>
       </c>
       <c r="B53" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>137381625</v>
       </c>
       <c r="B54" t="n">
-        <v>98298</v>
+        <v>98299</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 42971-2026 artfynd.xlsx
+++ b/artfynd/A 42971-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934385</v>
       </c>
       <c r="B2" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>136934394</v>
       </c>
       <c r="B11" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>136934382</v>
       </c>
       <c r="B31" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>136934383</v>
       </c>
       <c r="B32" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>136934384</v>
       </c>
       <c r="B33" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>136934387</v>
       </c>
       <c r="B34" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>136934388</v>
       </c>
       <c r="B35" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>136934389</v>
       </c>
       <c r="B36" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>136934390</v>
       </c>
       <c r="B37" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>136934391</v>
       </c>
       <c r="B38" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>136934392</v>
       </c>
       <c r="B39" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>136934396</v>
       </c>
       <c r="B40" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>136934398</v>
       </c>
       <c r="B41" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>137381620</v>
       </c>
       <c r="B42" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>137381622</v>
       </c>
       <c r="B43" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>137381623</v>
       </c>
       <c r="B44" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>137381626</v>
       </c>
       <c r="B45" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         <v>137381627</v>
       </c>
       <c r="B46" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>137381628</v>
       </c>
       <c r="B47" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         <v>137381629</v>
       </c>
       <c r="B48" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>137381630</v>
       </c>
       <c r="B49" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>137381632</v>
       </c>
       <c r="B50" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>137381634</v>
       </c>
       <c r="B51" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>137381635</v>
       </c>
       <c r="B52" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>137381636</v>
       </c>
       <c r="B53" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>137381625</v>
       </c>
       <c r="B54" t="n">
-        <v>98299</v>
+        <v>98302</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 42971-2026 artfynd.xlsx
+++ b/artfynd/A 42971-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934385</v>
       </c>
       <c r="B2" t="n">
-        <v>92185</v>
+        <v>92186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>136934394</v>
       </c>
       <c r="B11" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>136934382</v>
       </c>
       <c r="B31" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>136934383</v>
       </c>
       <c r="B32" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>136934384</v>
       </c>
       <c r="B33" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>136934387</v>
       </c>
       <c r="B34" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>136934388</v>
       </c>
       <c r="B35" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>136934389</v>
       </c>
       <c r="B36" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>136934390</v>
       </c>
       <c r="B37" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>136934391</v>
       </c>
       <c r="B38" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>136934392</v>
       </c>
       <c r="B39" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>136934396</v>
       </c>
       <c r="B40" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>136934398</v>
       </c>
       <c r="B41" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 42971-2026 artfynd.xlsx
+++ b/artfynd/A 42971-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934385</v>
       </c>
       <c r="B2" t="n">
-        <v>92186</v>
+        <v>92189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>136934394</v>
       </c>
       <c r="B11" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>136934397</v>
       </c>
       <c r="B13" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>136934382</v>
       </c>
       <c r="B31" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>136934383</v>
       </c>
       <c r="B32" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>136934384</v>
       </c>
       <c r="B33" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>136934387</v>
       </c>
       <c r="B34" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>136934388</v>
       </c>
       <c r="B35" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>136934389</v>
       </c>
       <c r="B36" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>136934390</v>
       </c>
       <c r="B37" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>136934391</v>
       </c>
       <c r="B38" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>136934392</v>
       </c>
       <c r="B39" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>136934396</v>
       </c>
       <c r="B40" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>136934398</v>
       </c>
       <c r="B41" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>137381620</v>
       </c>
       <c r="B42" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>137381622</v>
       </c>
       <c r="B43" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>137381623</v>
       </c>
       <c r="B44" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>137381626</v>
       </c>
       <c r="B45" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         <v>137381627</v>
       </c>
       <c r="B46" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>137381628</v>
       </c>
       <c r="B47" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         <v>137381629</v>
       </c>
       <c r="B48" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>137381630</v>
       </c>
       <c r="B49" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>137381632</v>
       </c>
       <c r="B50" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>137381634</v>
       </c>
       <c r="B51" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>137381635</v>
       </c>
       <c r="B52" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>137381636</v>
       </c>
       <c r="B53" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>137381625</v>
       </c>
       <c r="B54" t="n">
-        <v>98302</v>
+        <v>98306</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
